--- a/output/pdf_financials_xlsx/GEN.xlsx
+++ b/output/pdf_financials_xlsx/GEN.xlsx
@@ -3155,22 +3155,22 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.0399</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.0399</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.0399</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.0399</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.20027</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.213562</v>
       </c>
     </row>
     <row r="93">
@@ -5049,7 +5049,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -5741,7 +5745,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -6043,7 +6051,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GEN.xlsx
+++ b/output/pdf_financials_xlsx/GEN.xlsx
@@ -1476,25 +1476,25 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.099158</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.171808</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.137791</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.26155</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.25496</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.18232</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.036858</v>
       </c>
     </row>
     <row r="35">
@@ -1532,25 +1532,25 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.099158</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.171808</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.137791</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.26155</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.25496</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.18232</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.036858</v>
       </c>
     </row>
     <row r="37">
@@ -1874,19 +1874,19 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.137791</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.26155</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.269331</v>
+        <v>0.014371</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.251317</v>
+        <v>0.068997</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.060659</v>
+        <v>0.023801</v>
       </c>
     </row>
     <row r="49">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">

--- a/output/pdf_financials_xlsx/GEN.xlsx
+++ b/output/pdf_financials_xlsx/GEN.xlsx
@@ -617,7 +617,7 @@
         <v>0.031859</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.015663</v>
+        <v>0.017663</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0.101146</v>
@@ -7612,7 +7612,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -10912,7 +10916,11 @@
           <t>Directors fees (Note 6)</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
